--- a/public/assets/images/VendorEmailerTemplate.xlsx
+++ b/public/assets/images/VendorEmailerTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ajaz\Desktop\BulkMailer\bulk_emailer_frontend\public\asset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ajaz\Desktop\Admin-Mailcept\bulk_emailer_frontend\public\assets\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4B528C-57C5-4F20-967D-49267C987E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34F43E5-5ECF-47C9-B95C-060321934AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,16 +25,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>Email</t>
+  </si>
+  <si>
+    <t>Name</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,6 +66,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -85,11 +95,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -371,22 +382,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
     </row>
-    <row r="3" spans="1:1" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
     </row>
   </sheetData>
